--- a/human_validation/judge/kor/judge_D011_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S001_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,145 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요—저는 [의사명] 선생입니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 모든 게 한꺼번에 걱정돼서 도무지 멈출 수가 없어서 왔어요. 결혼생활, 직장에서 뒤처지고 있는 건 아닌지, 청구서들, 계속 못 끝내는 집안 프로젝트들… 그리고 제가 남편으로서도, 아빠로서도 실패하고 있다는 생각이 계속 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 느낌을 얼마나 오래 겪고 계신가요—이렇게 계속 걱정하는 게 몇 주째 이어지고 있나요, 아니면 6개월 이상 지속돼 온 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 지금 한 아홉 달쯤 됐어요. 직장에서 클라우드 마이그레이션이 본격화되면서, 그리고 집에서 다투는 일이 잦아지기 시작하면서부터 정말로 시작된 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 결혼생활, 직장, 청구서 같은 것들을 걱정하실 때, 애써 제쳐두려고 해도 그 걱정을 멈추거나 조절하기가 어려우신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네, 정말 멈추기가 힘들어요. 눈앞에 있는 코드에 집중해보려 하거나, 운동하면서 그냥 호흡에 집중해보려고 해도, 한 걱정이 다른 걱정으로 이어져요. 어느새 저는 스무 단계쯤 앞서 나가 있어요—나쁜 평가를 받으면 직장을 잃는다는 생각을 하고, 그러면 저 때문에 가족이 더 힘들어질 거라는 생각까지 하게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 걱정과 함께, 안절부절못하거나 곤두선 느낌, 근육 긴장, 피로, 수면의 어려움 같은 신체적인 증상도 알아채신 게 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 거의 하루 종일 몸이 팽팽하게 조여 있는 느낌이에요—어깨가 잠긴 것처럼 뻣뻣하고 뭔가에 대비하고 있는 느낌이죠. 회의 사이사이에 저도 모르게 서성거리고 있고, 체스 클럽에서는 가만히 앉아 있는 게 거의 불가능하게 느껴져서 말들을 계속 톡톡 건드리고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 걱정과 긴장 외에도, 기분이 가라앉거나 슬프거나, 예전에 즐기던 것들에 대한 흥미와 즐거움을 잃은 느낌도 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 대체로 슬프다기보다는 그냥 계속 스트레스받고 걱정하는 느낌에 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 직장 상황이나 결혼생활과는 전혀 상관없는 것들—건강이나 세상 돌아가는 일, 아니면 다른 일상적인 문제들에 대해서도 과도하게 걱정하시는 편인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네—직장이나 결혼생활만이 아니에요. 청구서, 계속 못 끝내는 집안 프로젝트들, 그리고 제가 어떻게든 가족을 실망시키고 있는 건 아닌가 하는 생각까지 한꺼번에 쌓이는 느낌이에요. 그중 뭐 하나도 끌 수가 없는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>진단명: 범불안장애 (D011)
 인구통계: 성별 남성 / 나이 35 / 직업상태 computer occupation / 최종학력 대학원 졸업
@@ -575,194 +705,36 @@
 증상 지속 기간: 9 months
 추가 요건: 
 주호소 증상 코드: S056
-배경 서술: 직장에서 고강도 클라우드 마이그레이션 작업이 진행되는 동안, 테렐과 그의 아내는 그가 끼니를 거르는 것, 끝내지 못한 집안 프로젝트, 밤늦은 코드 리뷰, 그리고 집 밖에서 교육이나 멘토링에 쓰는 시간에 대해 훨씬 더 자주 다투기 시작했다. 처음에는 일정에 대한 갈등이었던 것이 점차 9개월에 걸쳐 결혼생활, 직장 안정성, 재정, 가정 내 책임, 그리고 스스로 세운 기준에 부응하지 못하고 있는 건 아닌가 하는 전방위적인 걱정으로 번져갔다. 이 걱정은 그가 끄기 어려운 것이 되어 수면을 방해했고, 크로스핏이나 체스 클럽에서조차 긴장을 풀지 못하게 했으며, 스프린트 계획 회의와 코드 리뷰에서의 집중력을 눈에 띄게 저하시켰다. 그는 긴장된 인사평가 이후, 상사가 놓친 아키텍처 세부 사항들을 기록하고 테렐 본인이 직장 내 직원 지원 프로그램을 통해 도움을 요청하면서 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요—저는 [의사명] 선생입니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 모든 게 한꺼번에 걱정돼서 도무지 멈출 수가 없어서 왔어요. 결혼생활, 직장에서 뒤처지고 있는 건 아닌지, 청구서들, 계속 못 끝내는 집안 프로젝트들… 그리고 제가 남편으로서도, 아빠로서도 실패하고 있다는 생각이 계속 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 느낌을 얼마나 오래 겪고 계신가요—이렇게 계속 걱정하는 게 몇 주째 이어지고 있나요, 아니면 6개월 이상 지속돼 온 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 지금 한 아홉 달쯤 됐어요. 직장에서 클라우드 마이그레이션이 본격화되면서, 그리고 집에서 다투는 일이 잦아지기 시작하면서부터 정말로 시작된 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 결혼생활, 직장, 청구서 같은 것들을 걱정하실 때, 애써 제쳐두려고 해도 그 걱정을 멈추거나 조절하기가 어려우신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네, 정말 멈추기가 힘들어요. 눈앞에 있는 코드에 집중해보려 하거나, 운동하면서 그냥 호흡에 집중해보려고 해도, 한 걱정이 다른 걱정으로 이어져요. 어느새 저는 스무 단계쯤 앞서 나가 있어요—나쁜 평가를 받으면 직장을 잃는다는 생각을 하고, 그러면 저 때문에 가족이 더 힘들어질 거라는 생각까지 하게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 걱정과 함께, 안절부절못하거나 곤두선 느낌, 근육 긴장, 피로, 수면의 어려움 같은 신체적인 증상도 알아채신 게 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 거의 하루 종일 몸이 팽팽하게 조여 있는 느낌이에요—어깨가 잠긴 것처럼 뻣뻣하고 뭔가에 대비하고 있는 느낌이죠. 회의 사이사이에 저도 모르게 서성거리고 있고, 체스 클럽에서는 가만히 앉아 있는 게 거의 불가능하게 느껴져서 말들을 계속 톡톡 건드리고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 걱정과 긴장 외에도, 기분이 가라앉거나 슬프거나, 예전에 즐기던 것들에 대한 흥미와 즐거움을 잃은 느낌도 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 대체로 슬프다기보다는 그냥 계속 스트레스받고 걱정하는 느낌에 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 직장 상황이나 결혼생활과는 전혀 상관없는 것들—건강이나 세상 돌아가는 일, 아니면 다른 일상적인 문제들에 대해서도 과도하게 걱정하시는 편인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네—직장이나 결혼생활만이 아니에요. 청구서, 계속 못 끝내는 집안 프로젝트들, 그리고 제가 어떻게든 가족을 실망시키고 있는 건 아닌가 하는 생각까지 한꺼번에 쌓이는 느낌이에요. 그중 뭐 하나도 끌 수가 없는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+배경 서술: 직장에서 고강도 클라우드 마이그레이션 작업이 진행되는 동안, 테렐과 그의 아내는 그가 끼니를 거르는 것, 끝내지 못한 집안 프로젝트, 밤늦은 코드 리뷰, 그리고 집 밖에서 교육이나 멘토링에 쓰는 시간에 대해 훨씬 더 자주 다투기 시작했다. 처음에는 일정에 대한 갈등이었던 것이 점차 9개월에 걸쳐 결혼생활, 직장 안정성, 재정, 가정 내 책임, 그리고 스스로 세운 기준에 부응하지 못하고 있는 건 아닌가 하는 전방위적인 걱정으로 번져갔다. 이 걱정은 그가 끄기 어려운 것이 되어 수면을 방해했고, 크로스핏이나 체스 클럽에서조차 긴장을 풀지 못하게 했으며, 스프린트 계획 회의와 코드 리뷰에서의 집중력을 눈에 띄게 저하시켰다. 그는 긴장된 인사평가 이후, 상사가 놓친 아키텍처 세부 사항들을 기록하고 테렐 본인이 직장 내 직원 지원 프로그램을 통해 도움을 요청하면서 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S056 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.
+  - S057 통제 불가능한 걱정: 걱정을 멈추거나 조절하기 어렵다는 주관적 경험.
+  - S058 안절부절/긴장감: 안절부절못하거나 곤두선 느낌 또는 신경이 날카로운 느낌.
+  - S059 집중 곤란: 집중하는 데 어려움을 겪거나 머릿속이 하얘짐.</t>
+        </is>
+      </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 범불안장애 (D011, ICD: F41.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: anxiety_symptoms (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.; 통제 불가능한 걱정: 걱정을 멈추거나 조절하기 어렵다는 주관적 경험.; 안절부절/긴장감: 안절부절못하거나 곤두선 느낌 또는 신경이 날카로운 느낌.; 근육 긴장: 근육이 지속적으로 긴장되고 뻣뻣하며 불편감을 동반하는 상태.
-  누락: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 집중 곤란: 집중하는 데 어려움을 겪거나 머릿속이 하얘짐.; 과민성: 사소한 자극에도 민감하거나 날카롭게 반응하는 상태.</t>
+          <t>의사의 최종 진단: 범불안장애 (D011, ICD: F41.1)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: anxiety_symptoms (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.
+  - 통제 불가능한 걱정: 걱정을 멈추거나 조절하기 어렵다는 주관적 경험.
+  - 안절부절/긴장감: 안절부절못하거나 곤두선 느낌 또는 신경이 날카로운 느낌.
+  - 근육 긴장: 근육이 지속적으로 긴장되고 뻣뻣하며 불편감을 동반하는 상태.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D011_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S001_P002__claude-sonnet-5_kor.xlsx
@@ -691,6 +691,11 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -730,11 +735,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D011_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S001_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.6667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
